--- a/exports/trend_1d/FORTIS_full_report.xlsx
+++ b/exports/trend_1d/FORTIS_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q63"/>
+  <dimension ref="A1:U63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>8.289999999999999</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42118</v>
+        <v>42121</v>
       </c>
       <c r="H2" t="n">
-        <v>156</v>
+        <v>143.65</v>
       </c>
       <c r="I2" t="n">
         <v>155.1053967170577</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="K2" t="n">
-        <v>46.34</v>
+        <v>34.76</v>
       </c>
       <c r="L2" t="n">
         <v>1.88</v>
@@ -555,7 +578,7 @@
         <v>1.53</v>
       </c>
       <c r="N2" t="n">
-        <v>5.24</v>
+        <v>7.92</v>
       </c>
       <c r="O2" t="n">
         <v>1.62</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>4</v>
+      </c>
+      <c r="U2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>22.38</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42152</v>
+        <v>42153</v>
       </c>
       <c r="H3" t="n">
-        <v>161.55</v>
+        <v>174.4</v>
       </c>
       <c r="I3" t="n">
         <v>173.1985304182172</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K3" t="n">
-        <v>-12.46</v>
+        <v>-21.41</v>
       </c>
       <c r="L3" t="n">
         <v>23.74</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42124</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>17.65</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42236</v>
+        <v>42237</v>
       </c>
       <c r="H4" t="n">
-        <v>177.5</v>
+        <v>175.7</v>
       </c>
       <c r="I4" t="n">
         <v>175.8872062352682</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K4" t="n">
-        <v>1.78</v>
+        <v>0.75</v>
       </c>
       <c r="L4" t="n">
         <v>13.93</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>11.59</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42263</v>
+        <v>42265</v>
       </c>
       <c r="H5" t="n">
-        <v>161.55</v>
+        <v>178.1</v>
       </c>
       <c r="I5" t="n">
         <v>177.9271646306632</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K5" t="n">
-        <v>8.050000000000001</v>
+        <v>-1.37</v>
       </c>
       <c r="L5" t="n">
         <v>5.58</v>
@@ -726,7 +785,7 @@
         <v>2.12</v>
       </c>
       <c r="N5" t="n">
-        <v>7.11</v>
+        <v>10.24</v>
       </c>
       <c r="O5" t="n">
         <v>-1.01</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>18.31</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42410</v>
+        <v>42411</v>
       </c>
       <c r="H6" t="n">
-        <v>165.05</v>
+        <v>155</v>
       </c>
       <c r="I6" t="n">
         <v>163.9115032176273</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K6" t="n">
-        <v>-7.33</v>
+        <v>-12.97</v>
       </c>
       <c r="L6" t="n">
-        <v>13.71</v>
+        <v>14.85</v>
       </c>
       <c r="M6" t="n">
         <v>3.01</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42271</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>6</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>15.75</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42418</v>
+        <v>42419</v>
       </c>
       <c r="H7" t="n">
-        <v>156.8</v>
+        <v>175.7</v>
       </c>
       <c r="I7" t="n">
         <v>172.8410337941512</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.16</v>
+        <v>-13.35</v>
       </c>
       <c r="L7" t="n">
-        <v>6.42</v>
+        <v>16.71</v>
       </c>
       <c r="M7" t="n">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="N7" t="n">
-        <v>3.31</v>
+        <v>12.05</v>
       </c>
       <c r="O7" t="n">
         <v>-6.09</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>19.96</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42516</v>
+        <v>42517</v>
       </c>
       <c r="H8" t="n">
-        <v>173.15</v>
+        <v>164</v>
       </c>
       <c r="I8" t="n">
         <v>166.3254308326894</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.45</v>
+        <v>-6.66</v>
       </c>
       <c r="L8" t="n">
         <v>10.19</v>
       </c>
       <c r="M8" t="n">
-        <v>1.42</v>
+        <v>1.93</v>
       </c>
       <c r="N8" t="n">
-        <v>3.3</v>
+        <v>5.28</v>
       </c>
       <c r="O8" t="n">
         <v>12.05</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>11.94</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42565</v>
+        <v>42566</v>
       </c>
       <c r="H9" t="n">
-        <v>156.9</v>
+        <v>169.95</v>
       </c>
       <c r="I9" t="n">
         <v>167.8811053907098</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K9" t="n">
-        <v>4.33</v>
+        <v>-3.63</v>
       </c>
       <c r="L9" t="n">
-        <v>3.54</v>
+        <v>5.12</v>
       </c>
       <c r="M9" t="n">
         <v>1.29</v>
       </c>
       <c r="N9" t="n">
-        <v>2.46</v>
+        <v>8.32</v>
       </c>
       <c r="O9" t="n">
         <v>-5.28</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>12.42</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42632</v>
+        <v>42633</v>
       </c>
       <c r="H10" t="n">
-        <v>174.65</v>
+        <v>172.3</v>
       </c>
       <c r="I10" t="n">
         <v>172.8082182711037</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K10" t="n">
-        <v>2.77</v>
+        <v>1.38</v>
       </c>
       <c r="L10" t="n">
         <v>7.56</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>10.15</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42660</v>
+        <v>42661</v>
       </c>
       <c r="H11" t="n">
-        <v>178.2</v>
+        <v>182.75</v>
       </c>
       <c r="I11" t="n">
         <v>181.2082001312302</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.42</v>
+        <v>-6.07</v>
       </c>
       <c r="L11" t="n">
-        <v>9.109999999999999</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="M11" t="n">
         <v>4.98</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42642</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>10.5</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42684</v>
+        <v>42685</v>
       </c>
       <c r="H12" t="n">
-        <v>165.1</v>
+        <v>163.15</v>
       </c>
       <c r="I12" t="n">
         <v>163.5599181049465</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K12" t="n">
-        <v>-9.66</v>
+        <v>-10.73</v>
       </c>
       <c r="L12" t="n">
         <v>22.16</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>15.18</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42699</v>
+        <v>42702</v>
       </c>
       <c r="H13" t="n">
-        <v>176.45</v>
+        <v>183.45</v>
       </c>
       <c r="I13" t="n">
         <v>178.448472633557</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K13" t="n">
-        <v>-8.15</v>
+        <v>-12.44</v>
       </c>
       <c r="L13" t="n">
-        <v>8.800000000000001</v>
+        <v>13.85</v>
       </c>
       <c r="M13" t="n">
         <v>1.49</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>13.22</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42815</v>
+        <v>42816</v>
       </c>
       <c r="H14" t="n">
-        <v>179.55</v>
+        <v>174.4</v>
       </c>
       <c r="I14" t="n">
         <v>176.9266491317261</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.13</v>
+        <v>-4.93</v>
       </c>
       <c r="L14" t="n">
         <v>8.390000000000001</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>10.68</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42838</v>
+        <v>42842</v>
       </c>
       <c r="H15" t="n">
-        <v>185.45</v>
+        <v>202.75</v>
       </c>
       <c r="I15" t="n">
         <v>193.02287840503</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="K15" t="n">
-        <v>-6.34</v>
+        <v>-16.26</v>
       </c>
       <c r="L15" t="n">
-        <v>10.44</v>
+        <v>18.52</v>
       </c>
       <c r="M15" t="n">
         <v>0.85</v>
       </c>
       <c r="N15" t="n">
-        <v>4.76</v>
+        <v>9.33</v>
       </c>
       <c r="O15" t="n">
         <v>-2.87</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>13.5</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42874</v>
+        <v>42877</v>
       </c>
       <c r="H16" t="n">
-        <v>203.55</v>
+        <v>194.8</v>
       </c>
       <c r="I16" t="n">
         <v>196.6074993531527</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K16" t="n">
-        <v>0.39</v>
+        <v>-3.92</v>
       </c>
       <c r="L16" t="n">
         <v>8.359999999999999</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>15.09</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43063</v>
+        <v>43066</v>
       </c>
       <c r="H17" t="n">
-        <v>138.75</v>
+        <v>143</v>
       </c>
       <c r="I17" t="n">
         <v>141.7560609433031</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="K17" t="n">
-        <v>28.77</v>
+        <v>26.59</v>
       </c>
       <c r="L17" t="n">
         <v>5.88</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>129</v>
+        <v>130</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>7</v>
+      </c>
+      <c r="U17" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>13.98</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43080</v>
+        <v>43081</v>
       </c>
       <c r="H18" t="n">
-        <v>138.7</v>
+        <v>128</v>
       </c>
       <c r="I18" t="n">
         <v>128.2917245590317</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.01</v>
+        <v>-10.49</v>
       </c>
       <c r="L18" t="n">
-        <v>4.2</v>
+        <v>11.54</v>
       </c>
       <c r="M18" t="n">
         <v>3.07</v>
       </c>
       <c r="N18" t="n">
-        <v>5.55</v>
+        <v>7.71</v>
       </c>
       <c r="O18" t="n">
         <v>3.06</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>21.67</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43095</v>
+        <v>43096</v>
       </c>
       <c r="H19" t="n">
-        <v>150.35</v>
+        <v>158.1</v>
       </c>
       <c r="I19" t="n">
         <v>152.8170933586237</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K19" t="n">
-        <v>-17.46</v>
+        <v>-23.52</v>
       </c>
       <c r="L19" t="n">
-        <v>19.14</v>
+        <v>24.69</v>
       </c>
       <c r="M19" t="n">
         <v>1.95</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>14.95</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43115</v>
+        <v>43116</v>
       </c>
       <c r="H20" t="n">
-        <v>146.25</v>
+        <v>140.3</v>
       </c>
       <c r="I20" t="n">
         <v>143.3585776844354</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K20" t="n">
-        <v>-7.5</v>
+        <v>-11.26</v>
       </c>
       <c r="L20" t="n">
-        <v>9.199999999999999</v>
+        <v>12.08</v>
       </c>
       <c r="M20" t="n">
         <v>1.63</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>20.39</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43139</v>
+        <v>43140</v>
       </c>
       <c r="H21" t="n">
-        <v>126.05</v>
+        <v>148.6</v>
       </c>
       <c r="I21" t="n">
         <v>138.948407460102</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K21" t="n">
-        <v>10.16</v>
+        <v>-5.92</v>
       </c>
       <c r="L21" t="n">
         <v>14.08</v>
@@ -1638,7 +1889,7 @@
         <v>2.89</v>
       </c>
       <c r="N21" t="n">
-        <v>8.359999999999999</v>
+        <v>17.89</v>
       </c>
       <c r="O21" t="n">
         <v>-4.07</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>27.86</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43186</v>
+        <v>43187</v>
       </c>
       <c r="H22" t="n">
-        <v>142.25</v>
+        <v>123.35</v>
       </c>
       <c r="I22" t="n">
         <v>131.4455928919323</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.27</v>
+        <v>-16.99</v>
       </c>
       <c r="L22" t="n">
         <v>21.84</v>
       </c>
       <c r="M22" t="n">
-        <v>3.13</v>
+        <v>6.15</v>
       </c>
       <c r="N22" t="n">
-        <v>8.550000000000001</v>
+        <v>13.29</v>
       </c>
       <c r="O22" t="n">
         <v>17.89</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>30.44</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43220</v>
+        <v>43222</v>
       </c>
       <c r="H23" t="n">
-        <v>152.4</v>
+        <v>158.9</v>
       </c>
       <c r="I23" t="n">
         <v>157.8537999679186</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K23" t="n">
-        <v>-23.55</v>
+        <v>-28.82</v>
       </c>
       <c r="L23" t="n">
-        <v>27.6</v>
+        <v>30.12</v>
       </c>
       <c r="M23" t="n">
         <v>3.68</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,22 +2075,22 @@
         <v>11.9</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43262</v>
+        <v>43263</v>
       </c>
       <c r="H24" t="n">
-        <v>143.75</v>
+        <v>139.95</v>
       </c>
       <c r="I24" t="n">
         <v>140.9417111124191</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K24" t="n">
-        <v>-9.529999999999999</v>
+        <v>-11.93</v>
       </c>
       <c r="L24" t="n">
-        <v>11.14</v>
+        <v>12.84</v>
       </c>
       <c r="M24" t="n">
         <v>1.29</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>9.880000000000001</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43293</v>
+        <v>43294</v>
       </c>
       <c r="H25" t="n">
-        <v>142.2</v>
+        <v>147.8</v>
       </c>
       <c r="I25" t="n">
         <v>145.8302491557452</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.61</v>
+        <v>-5.61</v>
       </c>
       <c r="L25" t="n">
-        <v>4.61</v>
+        <v>6.79</v>
       </c>
       <c r="M25" t="n">
         <v>2.57</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>13.32</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43362</v>
+        <v>43364</v>
       </c>
       <c r="H26" t="n">
-        <v>142</v>
+        <v>137.25</v>
       </c>
       <c r="I26" t="n">
         <v>139.2456392853395</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.92</v>
+        <v>-7.14</v>
       </c>
       <c r="L26" t="n">
         <v>10.69</v>
@@ -1923,7 +2234,7 @@
         <v>1.47</v>
       </c>
       <c r="N26" t="n">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="O26" t="n">
         <v>3.94</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>9.470000000000001</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43416</v>
+        <v>43417</v>
       </c>
       <c r="H27" t="n">
-        <v>139.6</v>
+        <v>141.7</v>
       </c>
       <c r="I27" t="n">
         <v>141.3303595360806</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.71</v>
+        <v>-3.24</v>
       </c>
       <c r="L27" t="n">
-        <v>4.66</v>
+        <v>5.17</v>
       </c>
       <c r="M27" t="n">
         <v>4.21</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>8.640000000000001</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43447</v>
+        <v>43448</v>
       </c>
       <c r="H28" t="n">
-        <v>151.6</v>
+        <v>141.45</v>
       </c>
       <c r="I28" t="n">
         <v>144.5164448265618</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K28" t="n">
-        <v>6.99</v>
+        <v>-0.18</v>
       </c>
       <c r="L28" t="n">
-        <v>2.58</v>
+        <v>8.26</v>
       </c>
       <c r="M28" t="n">
         <v>0.57</v>
       </c>
       <c r="N28" t="n">
-        <v>0.85</v>
+        <v>6.7</v>
       </c>
       <c r="O28" t="n">
         <v>1.5</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>9.15</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43535</v>
+        <v>43536</v>
       </c>
       <c r="H29" t="n">
-        <v>135.45</v>
+        <v>141.8</v>
       </c>
       <c r="I29" t="n">
         <v>139.2375941521359</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K29" t="n">
-        <v>4.24</v>
+        <v>-0.25</v>
       </c>
       <c r="L29" t="n">
         <v>7.46</v>
@@ -2094,7 +2441,7 @@
         <v>0.9</v>
       </c>
       <c r="N29" t="n">
-        <v>2.42</v>
+        <v>4.69</v>
       </c>
       <c r="O29" t="n">
         <v>-6.7</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>4</v>
+      </c>
+      <c r="U29" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>7.04</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43594</v>
+        <v>43595</v>
       </c>
       <c r="H30" t="n">
-        <v>133</v>
+        <v>131.9</v>
       </c>
       <c r="I30" t="n">
         <v>132.8448819930464</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K30" t="n">
-        <v>-6.21</v>
+        <v>-6.98</v>
       </c>
       <c r="L30" t="n">
-        <v>6.7</v>
+        <v>7.62</v>
       </c>
       <c r="M30" t="n">
         <v>0.8</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>4.94</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43626</v>
+        <v>43627</v>
       </c>
       <c r="H31" t="n">
-        <v>127.25</v>
+        <v>132.55</v>
       </c>
       <c r="I31" t="n">
         <v>129.159801558539</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K31" t="n">
-        <v>3.53</v>
+        <v>-0.49</v>
       </c>
       <c r="L31" t="n">
-        <v>1.29</v>
+        <v>2.2</v>
       </c>
       <c r="M31" t="n">
         <v>1.28</v>
       </c>
       <c r="N31" t="n">
-        <v>3.92</v>
+        <v>4.17</v>
       </c>
       <c r="O31" t="n">
         <v>-0.83</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>8.359999999999999</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43671</v>
+        <v>43672</v>
       </c>
       <c r="H32" t="n">
-        <v>127</v>
+        <v>124.95</v>
       </c>
       <c r="I32" t="n">
         <v>126.1534715275592</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K32" t="n">
-        <v>-4.19</v>
+        <v>-5.73</v>
       </c>
       <c r="L32" t="n">
-        <v>4.9</v>
+        <v>6.41</v>
       </c>
       <c r="M32" t="n">
         <v>1.09</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>6.12</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43690</v>
+        <v>43691</v>
       </c>
       <c r="H33" t="n">
-        <v>118.6</v>
+        <v>127.7</v>
       </c>
       <c r="I33" t="n">
         <v>125.3455113539123</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K33" t="n">
-        <v>5.08</v>
+        <v>-2.2</v>
       </c>
       <c r="L33" t="n">
-        <v>1.64</v>
+        <v>3.24</v>
       </c>
       <c r="M33" t="n">
         <v>1.08</v>
       </c>
       <c r="N33" t="n">
-        <v>3.83</v>
+        <v>7.67</v>
       </c>
       <c r="O33" t="n">
         <v>-1.61</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>15.39</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43789</v>
+        <v>43790</v>
       </c>
       <c r="H34" t="n">
-        <v>142.5</v>
+        <v>140.1</v>
       </c>
       <c r="I34" t="n">
         <v>141.8597821748716</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K34" t="n">
-        <v>11.59</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="L34" t="n">
         <v>8.140000000000001</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>4</v>
+      </c>
+      <c r="U34" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>14.96</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43840</v>
+        <v>43843</v>
       </c>
       <c r="H35" t="n">
-        <v>137.9</v>
+        <v>143.15</v>
       </c>
       <c r="I35" t="n">
         <v>140.1679261633981</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K35" t="n">
-        <v>1.57</v>
+        <v>-2.18</v>
       </c>
       <c r="L35" t="n">
         <v>4.78</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>9.550000000000001</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43896</v>
+        <v>43899</v>
       </c>
       <c r="H36" t="n">
-        <v>149.3</v>
+        <v>143.85</v>
       </c>
       <c r="I36" t="n">
         <v>145.9978666224267</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K36" t="n">
-        <v>4.3</v>
+        <v>0.49</v>
       </c>
       <c r="L36" t="n">
         <v>4.05</v>
@@ -2493,7 +2924,7 @@
         <v>2.79</v>
       </c>
       <c r="N36" t="n">
-        <v>3.43</v>
+        <v>3.65</v>
       </c>
       <c r="O36" t="n">
         <v>3.81</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>15.29</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44004</v>
+        <v>44005</v>
       </c>
       <c r="H37" t="n">
-        <v>121.25</v>
+        <v>127.1</v>
       </c>
       <c r="I37" t="n">
         <v>124.6172536597116</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K37" t="n">
-        <v>15.71</v>
+        <v>11.64</v>
       </c>
       <c r="L37" t="n">
         <v>6.33</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>4</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>12.95</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44118</v>
+        <v>44119</v>
       </c>
       <c r="H38" t="n">
-        <v>129.9</v>
+        <v>126.85</v>
       </c>
       <c r="I38" t="n">
         <v>128.5345140911704</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K38" t="n">
-        <v>2.2</v>
+        <v>-0.2</v>
       </c>
       <c r="L38" t="n">
         <v>4.8</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>5</v>
+      </c>
+      <c r="U38" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -2643,25 +3110,25 @@
         <v>11.77</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44146</v>
+        <v>44147</v>
       </c>
       <c r="H39" t="n">
-        <v>131.4</v>
+        <v>135</v>
       </c>
       <c r="I39" t="n">
         <v>134.8052065365138</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K39" t="n">
-        <v>-3.59</v>
+        <v>-6.42</v>
       </c>
       <c r="L39" t="n">
-        <v>4.97</v>
+        <v>7.84</v>
       </c>
       <c r="M39" t="n">
-        <v>0.98</v>
+        <v>1.22</v>
       </c>
       <c r="N39" t="n">
         <v>3.75</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>9.01</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44491</v>
+        <v>44494</v>
       </c>
       <c r="H40" t="n">
-        <v>256.15</v>
+        <v>248.9</v>
       </c>
       <c r="I40" t="n">
         <v>250.1873820750767</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="K40" t="n">
-        <v>89.73999999999999</v>
+        <v>84.37</v>
       </c>
       <c r="L40" t="n">
         <v>2.67</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>234</v>
+        <v>235</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>12</v>
+      </c>
+      <c r="U40" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>13.5</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44512</v>
+        <v>44515</v>
       </c>
       <c r="H41" t="n">
-        <v>257.25</v>
+        <v>276.4</v>
       </c>
       <c r="I41" t="n">
         <v>271.0952655712568</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K41" t="n">
-        <v>-3.35</v>
+        <v>-11.05</v>
       </c>
       <c r="L41" t="n">
-        <v>9.960000000000001</v>
+        <v>12.78</v>
       </c>
       <c r="M41" t="n">
-        <v>1.15</v>
+        <v>3.4</v>
       </c>
       <c r="N41" t="n">
-        <v>6.75</v>
+        <v>7.44</v>
       </c>
       <c r="O41" t="n">
         <v>-2.83</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>14.42</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H42" t="n">
-        <v>276</v>
+        <v>266.25</v>
       </c>
       <c r="I42" t="n">
         <v>275.6576963045115</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.14</v>
+        <v>-3.67</v>
       </c>
       <c r="L42" t="n">
         <v>6.35</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>11.43</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44622</v>
+        <v>44623</v>
       </c>
       <c r="H43" t="n">
-        <v>246.65</v>
+        <v>267</v>
       </c>
       <c r="I43" t="n">
         <v>261.8457228635655</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K43" t="n">
-        <v>7.36</v>
+        <v>-0.28</v>
       </c>
       <c r="L43" t="n">
         <v>5.09</v>
@@ -2892,7 +3407,7 @@
         <v>1.66</v>
       </c>
       <c r="N43" t="n">
-        <v>3.45</v>
+        <v>8.25</v>
       </c>
       <c r="O43" t="n">
         <v>-3.53</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>14.54</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44686</v>
+        <v>44687</v>
       </c>
       <c r="H44" t="n">
-        <v>253.8</v>
+        <v>250.9</v>
       </c>
       <c r="I44" t="n">
         <v>250.9524708849423</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K44" t="n">
-        <v>-4.94</v>
+        <v>-6.03</v>
       </c>
       <c r="L44" t="n">
         <v>7.55</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>9.890000000000001</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44748</v>
+        <v>44749</v>
       </c>
       <c r="H45" t="n">
-        <v>238.1</v>
+        <v>253</v>
       </c>
       <c r="I45" t="n">
         <v>248.7046854624265</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K45" t="n">
-        <v>5.1</v>
+        <v>-0.84</v>
       </c>
       <c r="L45" t="n">
-        <v>0.7</v>
+        <v>1.51</v>
       </c>
       <c r="M45" t="n">
         <v>1.41</v>
       </c>
       <c r="N45" t="n">
-        <v>4.26</v>
+        <v>6.26</v>
       </c>
       <c r="O45" t="n">
         <v>-1.14</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>12.23</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44825</v>
+        <v>44826</v>
       </c>
       <c r="H46" t="n">
-        <v>311.35</v>
+        <v>265.55</v>
       </c>
       <c r="I46" t="n">
         <v>282.3593187133602</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K46" t="n">
-        <v>23.06</v>
+        <v>4.96</v>
       </c>
       <c r="L46" t="n">
         <v>5.42</v>
@@ -3063,7 +3614,7 @@
         <v>1.87</v>
       </c>
       <c r="N46" t="n">
-        <v>3.1</v>
+        <v>14.71</v>
       </c>
       <c r="O46" t="n">
         <v>6.26</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>28.44</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44876</v>
+        <v>44879</v>
       </c>
       <c r="H47" t="n">
-        <v>282.25</v>
+        <v>303.85</v>
       </c>
       <c r="I47" t="n">
         <v>295.2945408198266</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K47" t="n">
-        <v>-6.29</v>
+        <v>-14.42</v>
       </c>
       <c r="L47" t="n">
         <v>21.9</v>
       </c>
       <c r="M47" t="n">
-        <v>2.14</v>
+        <v>2.39</v>
       </c>
       <c r="N47" t="n">
-        <v>3.87</v>
+        <v>7.65</v>
       </c>
       <c r="O47" t="n">
         <v>-14.71</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>3</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,25 +3731,25 @@
         <v>11.87</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H48" t="n">
-        <v>280</v>
+        <v>272.15</v>
       </c>
       <c r="I48" t="n">
         <v>272.4975513637547</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K48" t="n">
-        <v>-7.85</v>
+        <v>-10.43</v>
       </c>
       <c r="L48" t="n">
-        <v>9.43</v>
+        <v>11.44</v>
       </c>
       <c r="M48" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.23</v>
       </c>
       <c r="N48" t="n">
         <v>2.94</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>9.640000000000001</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45058</v>
+        <v>45061</v>
       </c>
       <c r="H49" t="n">
-        <v>270.5</v>
+        <v>276.15</v>
       </c>
       <c r="I49" t="n">
         <v>273.8397745455786</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="K49" t="n">
-        <v>0.61</v>
+        <v>-1.47</v>
       </c>
       <c r="L49" t="n">
         <v>6.74</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>6</v>
+      </c>
+      <c r="U49" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>8.02</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45148</v>
+        <v>45149</v>
       </c>
       <c r="H50" t="n">
-        <v>323.8</v>
+        <v>317.95</v>
       </c>
       <c r="I50" t="n">
         <v>318.5991073576442</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K50" t="n">
-        <v>17.26</v>
+        <v>15.14</v>
       </c>
       <c r="L50" t="n">
         <v>2.95</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>4</v>
+      </c>
+      <c r="U50" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>11.17</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45239</v>
+        <v>45240</v>
       </c>
       <c r="H51" t="n">
-        <v>342.2</v>
+        <v>359.4</v>
       </c>
       <c r="I51" t="n">
         <v>346.631668337488</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K51" t="n">
-        <v>-7.63</v>
+        <v>-13.04</v>
       </c>
       <c r="L51" t="n">
-        <v>9.56</v>
+        <v>15.11</v>
       </c>
       <c r="M51" t="n">
         <v>1.41</v>
       </c>
       <c r="N51" t="n">
-        <v>3.49</v>
+        <v>5.03</v>
       </c>
       <c r="O51" t="n">
         <v>-1.81</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>9.6</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="H52" t="n">
-        <v>421.5</v>
+        <v>408</v>
       </c>
       <c r="I52" t="n">
         <v>413.2593552581267</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K52" t="n">
-        <v>17.28</v>
+        <v>13.52</v>
       </c>
       <c r="L52" t="n">
         <v>5.11</v>
@@ -3405,7 +4028,7 @@
         <v>1.41</v>
       </c>
       <c r="N52" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="O52" t="n">
         <v>5.03</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>4</v>
+      </c>
+      <c r="U52" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -3441,25 +4076,25 @@
         <v>11.45</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45379</v>
+        <v>45383</v>
       </c>
       <c r="H53" t="n">
-        <v>420.2</v>
+        <v>428.95</v>
       </c>
       <c r="I53" t="n">
         <v>424.4126549711019</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K53" t="n">
-        <v>-2.99</v>
+        <v>-5.13</v>
       </c>
       <c r="L53" t="n">
-        <v>3.92</v>
+        <v>5.37</v>
       </c>
       <c r="M53" t="n">
-        <v>0.99</v>
+        <v>1.38</v>
       </c>
       <c r="N53" t="n">
         <v>4.35</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>10.16</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45671</v>
+        <v>45672</v>
       </c>
       <c r="H54" t="n">
-        <v>663.55</v>
+        <v>651.3</v>
       </c>
       <c r="I54" t="n">
         <v>653.3215163610678</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K54" t="n">
-        <v>54.69</v>
+        <v>51.84</v>
       </c>
       <c r="L54" t="n">
         <v>5.35</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>197</v>
+        <v>198</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>10</v>
+      </c>
+      <c r="U54" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>12.42</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45692</v>
+        <v>45693</v>
       </c>
       <c r="H55" t="n">
-        <v>629.05</v>
+        <v>669.7</v>
       </c>
       <c r="I55" t="n">
         <v>657.9724036577264</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K55" t="n">
-        <v>3.42</v>
+        <v>-2.83</v>
       </c>
       <c r="L55" t="n">
         <v>4.47</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>15.72</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="H56" t="n">
-        <v>1044.6</v>
+        <v>1023.05</v>
       </c>
       <c r="I56" t="n">
         <v>1029.012654277012</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K56" t="n">
-        <v>55.98</v>
+        <v>52.76</v>
       </c>
       <c r="L56" t="n">
         <v>12.33</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>181</v>
+        <v>182</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>10</v>
+      </c>
+      <c r="U56" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>8.15</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="H57" t="n">
-        <v>915.45</v>
+        <v>945</v>
       </c>
       <c r="I57" t="n">
         <v>919.7789703495265</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K57" t="n">
-        <v>10.52</v>
+        <v>7.63</v>
       </c>
       <c r="L57" t="n">
         <v>2.53</v>
@@ -3690,7 +4373,7 @@
         <v>1.74</v>
       </c>
       <c r="N57" t="n">
-        <v>2.83</v>
+        <v>3.23</v>
       </c>
       <c r="O57" t="n">
         <v>-2.06</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>8.02</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H58" t="n">
-        <v>892.05</v>
+        <v>856.45</v>
       </c>
       <c r="I58" t="n">
         <v>881.431854704944</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K58" t="n">
-        <v>-5.6</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="L58" t="n">
-        <v>7.05</v>
+        <v>9.94</v>
       </c>
       <c r="M58" t="n">
         <v>0.4</v>
       </c>
       <c r="N58" t="n">
-        <v>2.53</v>
+        <v>3.99</v>
       </c>
       <c r="O58" t="n">
         <v>3.23</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>9.69</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="H59" t="n">
-        <v>891.85</v>
+        <v>918.85</v>
       </c>
       <c r="I59" t="n">
         <v>900.1667242299641</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K59" t="n">
-        <v>-4.13</v>
+        <v>-7.29</v>
       </c>
       <c r="L59" t="n">
-        <v>4.83</v>
+        <v>8.69</v>
       </c>
       <c r="M59" t="n">
         <v>2.03</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>9.119999999999999</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="H60" t="n">
-        <v>892.55</v>
+        <v>878.45</v>
       </c>
       <c r="I60" t="n">
         <v>885.480608771695</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K60" t="n">
-        <v>-2.86</v>
+        <v>-4.4</v>
       </c>
       <c r="L60" t="n">
-        <v>3.12</v>
+        <v>6.82</v>
       </c>
       <c r="M60" t="n">
         <v>4.13</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>9.6</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="H61" t="n">
-        <v>850.25</v>
+        <v>877.55</v>
       </c>
       <c r="I61" t="n">
         <v>861.4988563042619</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K61" t="n">
-        <v>3.21</v>
+        <v>0.1</v>
       </c>
       <c r="L61" t="n">
         <v>2.43</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>11.04</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="H62" t="n">
-        <v>935.2</v>
+        <v>900</v>
       </c>
       <c r="I62" t="n">
         <v>918.4792477978798</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K62" t="n">
-        <v>6.57</v>
+        <v>2.56</v>
       </c>
       <c r="L62" t="n">
         <v>2.51</v>
@@ -3975,7 +4718,7 @@
         <v>1.35</v>
       </c>
       <c r="N62" t="n">
-        <v>3.38</v>
+        <v>3.76</v>
       </c>
       <c r="O62" t="n">
         <v>3.21</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>5</v>
+      </c>
+      <c r="U62" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="63">
@@ -4035,6 +4790,14 @@
       <c r="Q63" t="n">
         <v>53</v>
       </c>
+      <c r="R63" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8993,7 +9756,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67.7</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="6">
@@ -9003,7 +9766,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7">
@@ -9013,7 +9776,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="8">
@@ -9023,7 +9786,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -9033,7 +9796,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10">
@@ -9043,7 +9806,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11">
@@ -9053,7 +9816,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
@@ -9063,7 +9826,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13">
@@ -9073,7 +9836,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32.8</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="14">
@@ -9083,7 +9846,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4.4</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="15">
@@ -9093,7 +9856,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8.4</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="16">
@@ -9103,7 +9866,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.26</v>
+        <v>-5.45</v>
       </c>
     </row>
     <row r="17">
@@ -9113,7 +9876,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>89.73999999999999</v>
+        <v>84.37</v>
       </c>
     </row>
     <row r="18">
@@ -9123,7 +9886,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>49.2</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="19">
@@ -9133,7 +9896,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.97</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -9143,7 +9906,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.35</v>
+        <v>7.56</v>
       </c>
     </row>
     <row r="21">
@@ -9153,7 +9916,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>27.6</v>
+        <v>30.12</v>
       </c>
     </row>
     <row r="22">
@@ -9163,7 +9926,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23">
@@ -9173,7 +9936,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24">
@@ -9183,7 +9946,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="25">
@@ -9203,7 +9966,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.75</v>
+        <v>6.11</v>
       </c>
     </row>
     <row r="27">
@@ -9213,7 +9976,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>11.82</v>
+        <v>17.89</v>
       </c>
     </row>
     <row r="28">
@@ -9223,7 +9986,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29">
